--- a/02_고전문헌_통합비교분석/중국침구3대서적_동일별명_및_24경혈쌍_주치_임상공통점_종합심층분석.xlsx
+++ b/02_고전문헌_통합비교분석/중국침구3대서적_동일별명_및_24경혈쌍_주치_임상공통점_종합심층분석.xlsx
@@ -637,7 +637,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>金門(김문)</t>
+          <t>金門(금문)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
